--- a/data_extactor/batch/451_500.xlsx
+++ b/data_extactor/batch/451_500.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F720E84A-B79F-448A-862D-3C354D6570D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23608F85-BE23-4E02-A165-57FF79E1D283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="535">
   <si>
     <t>29-1216.00</t>
   </si>
@@ -1513,6 +1513,123 @@
   </si>
   <si>
     <t>Adjust equipment to optimize viewing of the nervous system. | Assist in training technicians, medical students, residents, or other staff members. | Attach electrodes to patients, using adhesives. | Calibrate, troubleshoot, or repair equipment and correct malfunctions, as needed. | Collect patients' medical information needed to customize tests. | Conduct tests or studies such as electroencephalography (EEG), polysomnography (PSG), nerve conduction studies (NCS), electromyography (EMG), and intraoperative monitoring (IOM). | Conduct tests to determine cerebral death, the absence of brain activity, or the probability of recovery from a coma. | Explain testing procedures to patients, answering questions or reassuring patients, as needed. | Indicate artifacts or interferences derived from sources outside of the brain, such as poor electrode contact or patient movement, on electroneurodiagnostic recordings. | Measure patients' body parts and mark locations where electrodes are to be placed. | Measure visual, auditory, or somatosensory evoked potentials (EPs) to determine responses to stimuli. | Monitor patients during tests or surgeries, using electroencephalographs (EEG), evoked potential (EP) instruments, or video recording equipment. | Participate in research projects, conferences, or technical meetings. | Set up, program, or record montages or electrical combinations when testing peripheral nerve, spinal cord, subcortical, or cortical responses. | Submit reports to physicians summarizing test results. | Summarize technical data to assist physicians to diagnose brain, sleep, or nervous system disorders.</t>
+  </si>
+  <si>
+    <t>Attending Physician | Geriatrician | Infectious Disease Physician | Medical Doctor | Nephrologist | Occupational Medicine Physician | Oncologist | Physician | Pulmonologist | Rheumatologist</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | Medical procedure coding software | Microsoft Excel | Microsoft Word | Email software | Database software | Scheduling software | Microsoft Outlook | Web browser software | Microsoft Office software | Microsoft PowerPoint</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Critical Thinking | Speaking | Science | Monitoring | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Biology | Chemistry | Psychology | Customer and Personal Service | English Language | Therapy and Counseling | Education and Training | Administration and Management | Sociology and Anthropology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Family Medicine Physicians | General Internal Medicine Physicians | Emergency Medicine Physicians | Pediatricians, General | Cardiologists | Neurologists | Dermatologists | Allergists and Immunologists | Hospitalists | Urologists | Preventive Medicine Physicians | Sports Medicine Physicians | Physical Medicine and Rehabilitation Physicians | Physicians, Pathologists | Psychiatrists | Radiologists | Anesthesiologists | Surgeons, All Other | Physician Assistants | Health Specialties Teachers, Postsecondary</t>
+  </si>
+  <si>
+    <t>Diagnose and treat patients in medical specialties not classified separately. | Obtain and review patient histories, symptoms, and prior medical records. | Perform physical examinations and order diagnostic tests and imaging studies. | Interpret laboratory and imaging results to establish diagnoses. | Prescribe and administer medications, therapies, and treatment regimens. | Perform procedures within the scope of the medical specialty. | Monitor patient progress and modify treatment plans as conditions change. | Counsel patients and families on diagnoses, prognosis, and preventive care. | Refer patients to specialists and coordinate multidisciplinary care. | Document clinical findings, orders, and treatment in medical records. | Supervise residents, physician assistants, nurses, and clinical staff. | Comply with medical ethics, privacy regulations, and quality standards. | Participate in case reviews, quality improvement, and clinical research. | Maintain board certification and licensure through continuing medical education. | Advise on public health, occupational health, or institutional medical policy.</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Biology | Customer and Personal Service | English Language | Chemistry | Psychology | Education and Training | Administration and Management | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing | Control Precision | Depth Perception | Multilimb Coordination | Static Strength</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Exposed to Radiation | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Biology | Psychology | Customer and Personal Service | English Language | Chemistry | Therapy and Counseling | Education and Training | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing | Control Precision | Depth Perception | Multilimb Coordination</t>
+  </si>
+  <si>
+    <t>Cardiothoracic Surgeon | Colorectal Surgeon | General Surgeon | Neurological Surgeon | Plastic Surgeon | Surgeon | Thoracic Surgeon | Transplant Surgeon | Trauma Surgeon | Vascular Surgeon</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Biology | Chemistry | Customer and Personal Service | English Language | Psychology | Education and Training | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing | Control Precision | Depth Perception | Multilimb Coordination | Reaction Time</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Spend Time Making Repetitive Motions | Exposed to Radiation | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection</t>
+  </si>
+  <si>
+    <t>Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Ophthalmologists, Except Pediatric | Oral and Maxillofacial Surgeons | Urologists | Anesthesiologists | Emergency Medicine Physicians | Physicians, All Other | General Internal Medicine Physicians | Cardiologists | Neurologists | Physicians, Pathologists | Radiologists | Physician Assistants | Surgical Assistants | Surgical Technologists | Registered Nurses | Nurse Anesthetists | Health Specialties Teachers, Postsecondary | Medical and Health Services Managers</t>
+  </si>
+  <si>
+    <t>Perform surgery in specialties not classified separately. | Evaluate patients to determine whether surgical intervention is indicated. | Review diagnostic imaging, laboratory results, and medical histories before surgery. | Explain surgical procedures, risks, benefits, and alternatives to obtain informed consent. | Plan operative approach, positioning, instrumentation, and contingency measures. | Perform operative procedures using established and advanced surgical techniques. | Direct the surgical team, including assistants, nurses, and technologists. | Manage intraoperative complications and unexpected findings. | Prescribe and oversee postoperative care, pain management, and rehabilitation. | Monitor patients for surgical complications and coordinate corrective treatment. | Document operative reports, orders, and follow-up assessments. | Coordinate care with referring physicians, anesthesiologists, and specialists. | Participate in morbidity and mortality reviews and quality improvement. | Train and supervise surgical residents, fellows, and students. | Maintain surgical privileges, board certification, and continuing education.</t>
+  </si>
+  <si>
+    <t>Clinical Practitioner | Health Practitioner | Homeopathic Practitioner | Hyperbaric Medicine Practitioner | Massage Therapy Practitioner | Naprapath | Nutrition Practitioner | Sleep Medicine Practitioner | Traditional Medicine Practitioner | Wellness Practitioner</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | Medical procedure coding software | Microsoft Excel | Microsoft Word | Email software | Database software | Scheduling software | Microsoft Outlook | Web browser software | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Biology | Therapy and Counseling | Customer and Personal Service | Psychology | English Language | Chemistry | Education and Training</t>
+  </si>
+  <si>
+    <t>Acupuncturists | Naturopathic Physicians | Orthoptists | Chiropractors | Dietitians and Nutritionists | Optometrists | Podiatrists | Physician Assistants | Nurse Practitioners | Registered Nurses | Physicians, All Other | Therapists, All Other | Occupational Therapists | Physical Therapists | Exercise Physiologists | Athletic Trainers | Genetic Counselors | Health Education Specialists | Healthcare Practitioners and Technical Workers, All Other | Health Specialties Teachers, Postsecondary</t>
+  </si>
+  <si>
+    <t>Diagnose and treat patients in healthcare practices not classified separately. | Interview patients and record health histories, symptoms, and concerns. | Perform examinations and assessments within the scope of practice. | Formulate treatment plans and explain recommended interventions to patients. | Administer treatments, therapies, and preventive care services. | Monitor patient response to treatment and adjust care accordingly. | Advise patients on nutrition, lifestyle, and self-care practices. | Refer patients to physicians and specialists when conditions exceed scope of practice. | Maintain accurate clinical records and treatment documentation. | Comply with licensing, scope-of-practice, and patient privacy requirements. | Order and interpret diagnostic tests permitted within the discipline. | Maintain clean, safe treatment environments and sterilize equipment. | Educate patients and communities about health promotion and disease prevention. | Pursue continuing education to maintain credentials and clinical skills.</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Customer and Personal Service | Public Safety and Security | English Language | Psychology | Biology | Transportation | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing | Reaction Time | Static Strength | Trunk Strength | Stamina | Auditory Attention</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions | In an Enclosed Vehicle or Operate Enclosed Equipment | Outdoors, Exposed to All Weather Conditions | Dealing with Violent or Physically Aggressive People | Exposed to Contaminants | Spend Time Bending or Twisting Your Body | Exposed to Hazardous Conditions</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Customer and Personal Service | Public Safety and Security | English Language | Psychology | Biology | Chemistry | Transportation | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Computers and Electronics | English Language | Customer and Personal Service | Administration and Management | Law and Government | Biology | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Perceptual Speed | Flexibility of Closure | Written Expression</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Clinical Technician | Dialysis Technician | Health Technician | Medical Technician | Monitor Technician | Perfusion Technician | Polysomnographic Technician | Sterile Processing Technician | Telemetry Technician | Electroneurodiagnostic Technician</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Listening | Speaking | Mathematics | Active Learning</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Biology | Customer and Personal Service | English Language | Computers and Electronics | Chemistry | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing | Control Precision | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Cardiovascular Technologists and Technicians | Diagnostic Medical Sonographers | Radiologic Technologists and Technicians | Magnetic Resonance Imaging Technologists | Nuclear Medicine Technologists | Neurodiagnostic Technologists | Surgical Technologists | Psychiatric Technicians | Pharmacy Technicians | Dietetic Technicians | Ophthalmic Medical Technicians | Endoscopy Technicians | Medical Equipment Preparers | Phlebotomists | Licensed Practical and Licensed Vocational Nurses | Registered Nurses | Medical Dosimetrists | Healthcare Practitioners and Technical Workers, All Other</t>
+  </si>
+  <si>
+    <t>Perform health technology duties in specialties not classified separately. | Operate diagnostic, monitoring, and treatment equipment according to protocol. | Prepare patients for procedures and explain what to expect. | Monitor patients during procedures and report abnormal findings to clinicians. | Calibrate, test, and maintain clinical equipment and troubleshoot malfunctions. | Collect, label, and process specimens and samples. | Record test results, readings, and observations in patient records. | Follow infection control, sterilization, and safety procedures. | Maintain inventories of supplies, reagents, and disposables. | Assist physicians and nurses during clinical procedures. | Verify patient identity and confirm orders before performing procedures. | Maintain quality control logs and participate in accreditation activities. | Instruct patients on preparation and aftercare instructions. | Complete continuing education to maintain certification and competency.</t>
   </si>
 </sst>
 </file>
@@ -2085,8 +2202,32 @@
       <c r="B8" t="s">
         <v>78</v>
       </c>
+      <c r="C8" t="s">
+        <v>496</v>
+      </c>
+      <c r="D8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E8" t="s">
+        <v>498</v>
+      </c>
+      <c r="F8" t="s">
+        <v>499</v>
+      </c>
+      <c r="G8" t="s">
+        <v>500</v>
+      </c>
+      <c r="H8" t="s">
+        <v>501</v>
+      </c>
+      <c r="I8" t="s">
+        <v>502</v>
+      </c>
       <c r="J8" t="s">
         <v>79</v>
+      </c>
+      <c r="K8" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2347,6 +2488,18 @@
       <c r="D16" t="s">
         <v>160</v>
       </c>
+      <c r="E16" t="s">
+        <v>498</v>
+      </c>
+      <c r="F16" t="s">
+        <v>504</v>
+      </c>
+      <c r="G16" t="s">
+        <v>505</v>
+      </c>
+      <c r="H16" t="s">
+        <v>506</v>
+      </c>
       <c r="I16" t="s">
         <v>161</v>
       </c>
@@ -2370,6 +2523,18 @@
       <c r="D17" t="s">
         <v>160</v>
       </c>
+      <c r="E17" t="s">
+        <v>498</v>
+      </c>
+      <c r="F17" t="s">
+        <v>507</v>
+      </c>
+      <c r="G17" t="s">
+        <v>508</v>
+      </c>
+      <c r="H17" t="s">
+        <v>506</v>
+      </c>
       <c r="I17" t="s">
         <v>167</v>
       </c>
@@ -2387,8 +2552,32 @@
       <c r="B18" t="s">
         <v>171</v>
       </c>
+      <c r="C18" t="s">
+        <v>509</v>
+      </c>
+      <c r="D18" t="s">
+        <v>497</v>
+      </c>
+      <c r="E18" t="s">
+        <v>498</v>
+      </c>
+      <c r="F18" t="s">
+        <v>510</v>
+      </c>
+      <c r="G18" t="s">
+        <v>511</v>
+      </c>
+      <c r="H18" t="s">
+        <v>512</v>
+      </c>
+      <c r="I18" t="s">
+        <v>513</v>
+      </c>
       <c r="J18" t="s">
         <v>172</v>
+      </c>
+      <c r="K18" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -2468,8 +2657,32 @@
       <c r="B21" t="s">
         <v>196</v>
       </c>
+      <c r="C21" t="s">
+        <v>515</v>
+      </c>
+      <c r="D21" t="s">
+        <v>516</v>
+      </c>
+      <c r="E21" t="s">
+        <v>498</v>
+      </c>
+      <c r="F21" t="s">
+        <v>517</v>
+      </c>
+      <c r="G21" t="s">
+        <v>500</v>
+      </c>
+      <c r="H21" t="s">
+        <v>501</v>
+      </c>
+      <c r="I21" t="s">
+        <v>518</v>
+      </c>
       <c r="J21" t="s">
         <v>197</v>
+      </c>
+      <c r="K21" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -2975,6 +3188,18 @@
       <c r="D36" t="s">
         <v>354</v>
       </c>
+      <c r="E36" t="s">
+        <v>498</v>
+      </c>
+      <c r="F36" t="s">
+        <v>520</v>
+      </c>
+      <c r="G36" t="s">
+        <v>521</v>
+      </c>
+      <c r="H36" t="s">
+        <v>522</v>
+      </c>
       <c r="I36" t="s">
         <v>355</v>
       </c>
@@ -2998,6 +3223,18 @@
       <c r="D37" t="s">
         <v>361</v>
       </c>
+      <c r="E37" t="s">
+        <v>498</v>
+      </c>
+      <c r="F37" t="s">
+        <v>523</v>
+      </c>
+      <c r="G37" t="s">
+        <v>521</v>
+      </c>
+      <c r="H37" t="s">
+        <v>522</v>
+      </c>
       <c r="I37" t="s">
         <v>362</v>
       </c>
@@ -3266,6 +3503,18 @@
       <c r="D45" t="s">
         <v>445</v>
       </c>
+      <c r="E45" t="s">
+        <v>524</v>
+      </c>
+      <c r="F45" t="s">
+        <v>525</v>
+      </c>
+      <c r="G45" t="s">
+        <v>526</v>
+      </c>
+      <c r="H45" t="s">
+        <v>527</v>
+      </c>
       <c r="I45" t="s">
         <v>446</v>
       </c>
@@ -3388,8 +3637,32 @@
       <c r="B49" t="s">
         <v>483</v>
       </c>
+      <c r="C49" t="s">
+        <v>528</v>
+      </c>
+      <c r="D49" t="s">
+        <v>516</v>
+      </c>
+      <c r="E49" t="s">
+        <v>529</v>
+      </c>
+      <c r="F49" t="s">
+        <v>530</v>
+      </c>
+      <c r="G49" t="s">
+        <v>531</v>
+      </c>
+      <c r="H49" t="s">
+        <v>532</v>
+      </c>
+      <c r="I49" t="s">
+        <v>533</v>
+      </c>
       <c r="J49" t="s">
         <v>484</v>
+      </c>
+      <c r="K49" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
